--- a/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.3.xlsx
+++ b/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.3.xlsx
@@ -3539,7 +3539,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>no_dangling_node</t>
+          <t>no_dangling_node (hydroobject-eindpunt is verbonden met beginpunt van een ander hydroobject)</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">

--- a/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.3.xlsx
+++ b/validation_rules/overzichten_ValidationRules/overzicht_ValidationRules_1.3.xlsx
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>left=maximalehoogteopening, right=kunstwerkopening_hoogte_m</t>
+          <t>left=hoogteopening, right=kunstwerkopening_hoogte_m</t>
         </is>
       </c>
     </row>
